--- a/output/yearly_population_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_77_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6279</v>
+        <v>6264</v>
       </c>
       <c r="C2" t="n">
-        <v>7890</v>
+        <v>5930</v>
       </c>
       <c r="D2" t="n">
-        <v>23347</v>
+        <v>23845</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4090</v>
+        <v>4075</v>
       </c>
       <c r="C3" t="n">
-        <v>7091</v>
+        <v>6480</v>
       </c>
       <c r="D3" t="n">
-        <v>10736</v>
+        <v>14054</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3107</v>
+        <v>3283</v>
       </c>
       <c r="C4" t="n">
-        <v>5315</v>
+        <v>5930</v>
       </c>
       <c r="D4" t="n">
-        <v>5564</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1959</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>3686</v>
+        <v>4273</v>
       </c>
       <c r="D5" t="n">
-        <v>2366</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>1146</v>
       </c>
       <c r="C6" t="n">
-        <v>2698</v>
+        <v>2744</v>
       </c>
       <c r="D6" t="n">
-        <v>1116</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>455</v>
+        <v>554</v>
       </c>
       <c r="C7" t="n">
-        <v>1554</v>
+        <v>1313</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>686</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>779</v>
+        <v>545</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7072</v>
+        <v>8696</v>
       </c>
       <c r="C2" t="n">
-        <v>11826</v>
+        <v>6986</v>
       </c>
       <c r="D2" t="n">
-        <v>22961</v>
+        <v>22065</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4146</v>
+        <v>4118</v>
       </c>
       <c r="C3" t="n">
-        <v>6617</v>
+        <v>5482</v>
       </c>
       <c r="D3" t="n">
-        <v>11729</v>
+        <v>14441</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3033</v>
+        <v>3108</v>
       </c>
       <c r="C4" t="n">
-        <v>6022</v>
+        <v>6013</v>
       </c>
       <c r="D4" t="n">
-        <v>6185</v>
+        <v>8356</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2197</v>
+        <v>2279</v>
       </c>
       <c r="C5" t="n">
-        <v>4391</v>
+        <v>4963</v>
       </c>
       <c r="D5" t="n">
-        <v>2815</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1307</v>
+        <v>1380</v>
       </c>
       <c r="C6" t="n">
-        <v>3099</v>
+        <v>3380</v>
       </c>
       <c r="D6" t="n">
-        <v>1282</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>638</v>
+        <v>724</v>
       </c>
       <c r="C7" t="n">
-        <v>2080</v>
+        <v>1957</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="C8" t="n">
-        <v>1112</v>
+        <v>870</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C9" t="n">
-        <v>545</v>
+        <v>386</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>277</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9489</v>
+        <v>9763</v>
       </c>
       <c r="C2" t="n">
-        <v>9640</v>
+        <v>7522</v>
       </c>
       <c r="D2" t="n">
-        <v>20218</v>
+        <v>25098</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4361</v>
+        <v>4818</v>
       </c>
       <c r="C3" t="n">
-        <v>7813</v>
+        <v>5412</v>
       </c>
       <c r="D3" t="n">
-        <v>12397</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2979</v>
+        <v>3001</v>
       </c>
       <c r="C4" t="n">
-        <v>6107</v>
+        <v>5595</v>
       </c>
       <c r="D4" t="n">
-        <v>6789</v>
+        <v>9036</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2260</v>
+        <v>2327</v>
       </c>
       <c r="C5" t="n">
-        <v>5019</v>
+        <v>5313</v>
       </c>
       <c r="D5" t="n">
-        <v>3247</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1536</v>
+        <v>1586</v>
       </c>
       <c r="C6" t="n">
-        <v>3585</v>
+        <v>3969</v>
       </c>
       <c r="D6" t="n">
-        <v>1473</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>811</v>
+        <v>887</v>
       </c>
       <c r="C7" t="n">
-        <v>2508</v>
+        <v>2522</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>426</v>
       </c>
       <c r="C8" t="n">
-        <v>1489</v>
+        <v>1306</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="C9" t="n">
-        <v>761</v>
+        <v>567</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>379</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
         <v>256</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8493</v>
+        <v>8847</v>
       </c>
       <c r="C2" t="n">
-        <v>6478</v>
+        <v>5114</v>
       </c>
       <c r="D2" t="n">
-        <v>16488</v>
+        <v>20634</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5361</v>
+        <v>5635</v>
       </c>
       <c r="C3" t="n">
-        <v>11138</v>
+        <v>8354</v>
       </c>
       <c r="D3" t="n">
-        <v>13607</v>
+        <v>16023</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2088</v>
+        <v>2150</v>
       </c>
       <c r="C4" t="n">
-        <v>8277</v>
+        <v>8215</v>
       </c>
       <c r="D4" t="n">
-        <v>6710</v>
+        <v>8945</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1465</v>
       </c>
       <c r="C5" t="n">
-        <v>3513</v>
+        <v>3889</v>
       </c>
       <c r="D5" t="n">
-        <v>2347</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>749</v>
+        <v>819</v>
       </c>
       <c r="C6" t="n">
-        <v>2457</v>
+        <v>2471</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="C7" t="n">
-        <v>1459</v>
+        <v>1279</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>745</v>
+        <v>555</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>371</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
         <v>250</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5041</v>
+        <v>5326</v>
       </c>
       <c r="C2" t="n">
-        <v>2734</v>
+        <v>2906</v>
       </c>
       <c r="D2" t="n">
-        <v>11361</v>
+        <v>14863</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5754</v>
+        <v>6022</v>
       </c>
       <c r="C3" t="n">
-        <v>8092</v>
+        <v>6217</v>
       </c>
       <c r="D3" t="n">
-        <v>13346</v>
+        <v>15727</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2915</v>
+        <v>3035</v>
       </c>
       <c r="C4" t="n">
-        <v>9795</v>
+        <v>8346</v>
       </c>
       <c r="D4" t="n">
-        <v>7694</v>
+        <v>9931</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1590</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>5620</v>
+        <v>5822</v>
       </c>
       <c r="D5" t="n">
-        <v>2865</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="C6" t="n">
-        <v>2957</v>
+        <v>3124</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>369</v>
       </c>
       <c r="C7" t="n">
-        <v>1870</v>
+        <v>1705</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>972</v>
+        <v>767</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>434</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4811</v>
+        <v>6086</v>
       </c>
       <c r="C2" t="n">
-        <v>10359</v>
+        <v>8003</v>
       </c>
       <c r="D2" t="n">
-        <v>16063</v>
+        <v>16774</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4568</v>
+        <v>4807</v>
       </c>
       <c r="C3" t="n">
-        <v>4888</v>
+        <v>4096</v>
       </c>
       <c r="D3" t="n">
-        <v>12141</v>
+        <v>14520</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3598</v>
+        <v>3706</v>
       </c>
       <c r="C4" t="n">
-        <v>8741</v>
+        <v>7109</v>
       </c>
       <c r="D4" t="n">
-        <v>8436</v>
+        <v>10630</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1919</v>
+        <v>1989</v>
       </c>
       <c r="C5" t="n">
-        <v>7507</v>
+        <v>6968</v>
       </c>
       <c r="D5" t="n">
-        <v>3565</v>
+        <v>4583</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1104</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>4183</v>
+        <v>4310</v>
       </c>
       <c r="D6" t="n">
-        <v>1224</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>542</v>
       </c>
       <c r="C7" t="n">
-        <v>2366</v>
+        <v>2346</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>1350</v>
+        <v>1160</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>643</v>
+        <v>498</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2835</v>
+        <v>3580</v>
       </c>
       <c r="C2" t="n">
-        <v>4751</v>
+        <v>3674</v>
       </c>
       <c r="D2" t="n">
-        <v>11074</v>
+        <v>11574</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4501</v>
+        <v>4982</v>
       </c>
       <c r="C3" t="n">
-        <v>6613</v>
+        <v>5308</v>
       </c>
       <c r="D3" t="n">
-        <v>12288</v>
+        <v>14423</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3947</v>
+        <v>4098</v>
       </c>
       <c r="C4" t="n">
-        <v>8103</v>
+        <v>6631</v>
       </c>
       <c r="D4" t="n">
-        <v>8974</v>
+        <v>11234</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1997</v>
+        <v>2065</v>
       </c>
       <c r="C5" t="n">
-        <v>8909</v>
+        <v>8068</v>
       </c>
       <c r="D5" t="n">
-        <v>3844</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>5045</v>
+        <v>5149</v>
       </c>
       <c r="D6" t="n">
-        <v>1203</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>2499</v>
+        <v>2336</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1053</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>253</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4659</v>
+        <v>4161</v>
       </c>
       <c r="C2" t="n">
-        <v>8630</v>
+        <v>4105</v>
       </c>
       <c r="D2" t="n">
-        <v>15281</v>
+        <v>13572</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>3749</v>
       </c>
       <c r="C3" t="n">
-        <v>5112</v>
+        <v>4046</v>
       </c>
       <c r="D3" t="n">
-        <v>11297</v>
+        <v>13066</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3686</v>
+        <v>3932</v>
       </c>
       <c r="C4" t="n">
-        <v>7297</v>
+        <v>5921</v>
       </c>
       <c r="D4" t="n">
-        <v>9242</v>
+        <v>11412</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2465</v>
+        <v>2554</v>
       </c>
       <c r="C5" t="n">
-        <v>8360</v>
+        <v>7329</v>
       </c>
       <c r="D5" t="n">
-        <v>4552</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>1267</v>
       </c>
       <c r="C6" t="n">
-        <v>6765</v>
+        <v>6385</v>
       </c>
       <c r="D6" t="n">
-        <v>1542</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="C7" t="n">
-        <v>3545</v>
+        <v>3488</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1622</v>
+        <v>1428</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>453</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3087</v>
+        <v>3016</v>
       </c>
       <c r="C2" t="n">
-        <v>4095</v>
+        <v>2704</v>
       </c>
       <c r="D2" t="n">
-        <v>10797</v>
+        <v>10007</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3254</v>
+        <v>3402</v>
       </c>
       <c r="C3" t="n">
-        <v>5904</v>
+        <v>3691</v>
       </c>
       <c r="D3" t="n">
-        <v>11160</v>
+        <v>12415</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3277</v>
+        <v>3569</v>
       </c>
       <c r="C4" t="n">
-        <v>6453</v>
+        <v>5194</v>
       </c>
       <c r="D4" t="n">
-        <v>9325</v>
+        <v>11396</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2703</v>
+        <v>2823</v>
       </c>
       <c r="C5" t="n">
-        <v>8119</v>
+        <v>6944</v>
       </c>
       <c r="D5" t="n">
-        <v>5041</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1408</v>
+        <v>1490</v>
       </c>
       <c r="C6" t="n">
-        <v>7540</v>
+        <v>6944</v>
       </c>
       <c r="D6" t="n">
-        <v>1813</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>4575</v>
+        <v>4401</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2087</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>538</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5156</v>
+        <v>4717</v>
       </c>
       <c r="C2" t="n">
-        <v>6979</v>
+        <v>6166</v>
       </c>
       <c r="D2" t="n">
-        <v>19526</v>
+        <v>15278</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2688</v>
+        <v>2747</v>
       </c>
       <c r="C3" t="n">
-        <v>4648</v>
+        <v>2922</v>
       </c>
       <c r="D3" t="n">
-        <v>10402</v>
+        <v>11331</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2840</v>
+        <v>3050</v>
       </c>
       <c r="C4" t="n">
-        <v>6024</v>
+        <v>4436</v>
       </c>
       <c r="D4" t="n">
-        <v>9305</v>
+        <v>11196</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2672</v>
+        <v>2807</v>
       </c>
       <c r="C5" t="n">
-        <v>7262</v>
+        <v>6077</v>
       </c>
       <c r="D5" t="n">
-        <v>5463</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1710</v>
+        <v>1812</v>
       </c>
       <c r="C6" t="n">
-        <v>7776</v>
+        <v>6884</v>
       </c>
       <c r="D6" t="n">
-        <v>2174</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="C7" t="n">
-        <v>5677</v>
+        <v>5414</v>
       </c>
       <c r="D7" t="n">
-        <v>871</v>
+        <v>978</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>2984</v>
+        <v>2799</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1109</v>
+        <v>1006</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4899</v>
+        <v>6977</v>
       </c>
       <c r="C2" t="n">
-        <v>6703</v>
+        <v>3011</v>
       </c>
       <c r="D2" t="n">
-        <v>9727</v>
+        <v>19542</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3687</v>
+        <v>3377</v>
       </c>
       <c r="C2" t="n">
-        <v>4019</v>
+        <v>3502</v>
       </c>
       <c r="D2" t="n">
-        <v>14371</v>
+        <v>11244</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3663</v>
+        <v>3717</v>
       </c>
       <c r="C3" t="n">
-        <v>5534</v>
+        <v>3927</v>
       </c>
       <c r="D3" t="n">
-        <v>11860</v>
+        <v>12607</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3895</v>
+        <v>4152</v>
       </c>
       <c r="C4" t="n">
-        <v>8504</v>
+        <v>6433</v>
       </c>
       <c r="D4" t="n">
-        <v>9618</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1654</v>
+        <v>1752</v>
       </c>
       <c r="C5" t="n">
-        <v>10837</v>
+        <v>9296</v>
       </c>
       <c r="D5" t="n">
-        <v>4998</v>
+        <v>6298</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>538</v>
+        <v>592</v>
       </c>
       <c r="C6" t="n">
-        <v>7087</v>
+        <v>6722</v>
       </c>
       <c r="D6" t="n">
-        <v>1807</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>2924</v>
+        <v>2743</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1086</v>
+        <v>985</v>
       </c>
       <c r="D8" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5972</v>
+        <v>7665</v>
       </c>
       <c r="C2" t="n">
-        <v>4229</v>
+        <v>3578</v>
       </c>
       <c r="D2" t="n">
-        <v>12513</v>
+        <v>16917</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2082</v>
+        <v>2963</v>
       </c>
       <c r="C3" t="n">
-        <v>3378</v>
+        <v>1517</v>
       </c>
       <c r="D3" t="n">
-        <v>2273</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4249</v>
+        <v>5137</v>
       </c>
       <c r="C2" t="n">
-        <v>4036</v>
+        <v>7173</v>
       </c>
       <c r="D2" t="n">
-        <v>19360</v>
+        <v>22096</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3305</v>
+        <v>4364</v>
       </c>
       <c r="C3" t="n">
-        <v>3329</v>
+        <v>2314</v>
       </c>
       <c r="D3" t="n">
-        <v>3826</v>
+        <v>5816</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>938</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="n">
-        <v>2054</v>
+        <v>933</v>
       </c>
       <c r="D4" t="n">
-        <v>1639</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6218</v>
+        <v>5218</v>
       </c>
       <c r="C2" t="n">
-        <v>6710</v>
+        <v>6217</v>
       </c>
       <c r="D2" t="n">
-        <v>19223</v>
+        <v>25285</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3101</v>
+        <v>3909</v>
       </c>
       <c r="C3" t="n">
-        <v>3215</v>
+        <v>4296</v>
       </c>
       <c r="D3" t="n">
-        <v>6035</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1795</v>
+        <v>2407</v>
       </c>
       <c r="C4" t="n">
-        <v>2733</v>
+        <v>1695</v>
       </c>
       <c r="D4" t="n">
-        <v>2009</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>445</v>
+        <v>603</v>
       </c>
       <c r="C5" t="n">
-        <v>1216</v>
+        <v>606</v>
       </c>
       <c r="D5" t="n">
-        <v>1221</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6060</v>
+        <v>5738</v>
       </c>
       <c r="C2" t="n">
-        <v>7457</v>
+        <v>9453</v>
       </c>
       <c r="D2" t="n">
-        <v>16120</v>
+        <v>25782</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3738</v>
+        <v>3727</v>
       </c>
       <c r="C3" t="n">
-        <v>4386</v>
+        <v>4599</v>
       </c>
       <c r="D3" t="n">
-        <v>7614</v>
+        <v>10065</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2067</v>
+        <v>2693</v>
       </c>
       <c r="C4" t="n">
-        <v>2939</v>
+        <v>3041</v>
       </c>
       <c r="D4" t="n">
-        <v>2662</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>933</v>
+        <v>1234</v>
       </c>
       <c r="C5" t="n">
-        <v>1991</v>
+        <v>1168</v>
       </c>
       <c r="D5" t="n">
-        <v>1327</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>322</v>
       </c>
       <c r="C6" t="n">
-        <v>761</v>
+        <v>453</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7518</v>
+        <v>8026</v>
       </c>
       <c r="C2" t="n">
-        <v>5251</v>
+        <v>6993</v>
       </c>
       <c r="D2" t="n">
-        <v>17481</v>
+        <v>23961</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3556</v>
+        <v>3464</v>
       </c>
       <c r="C3" t="n">
-        <v>4900</v>
+        <v>5799</v>
       </c>
       <c r="D3" t="n">
-        <v>7875</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1812</v>
+        <v>1980</v>
       </c>
       <c r="C4" t="n">
-        <v>3076</v>
+        <v>3171</v>
       </c>
       <c r="D4" t="n">
-        <v>3017</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>782</v>
+        <v>1025</v>
       </c>
       <c r="C5" t="n">
-        <v>1806</v>
+        <v>1580</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>283</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>939</v>
+        <v>545</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>257</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5657</v>
+        <v>6455</v>
       </c>
       <c r="C2" t="n">
-        <v>9989</v>
+        <v>9972</v>
       </c>
       <c r="D2" t="n">
-        <v>19285</v>
+        <v>25106</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4641</v>
+        <v>4790</v>
       </c>
       <c r="C3" t="n">
-        <v>4376</v>
+        <v>5584</v>
       </c>
       <c r="D3" t="n">
-        <v>8973</v>
+        <v>12491</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2377</v>
+        <v>2373</v>
       </c>
       <c r="C4" t="n">
-        <v>4150</v>
+        <v>4719</v>
       </c>
       <c r="D4" t="n">
-        <v>3951</v>
+        <v>5359</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1156</v>
+        <v>1350</v>
       </c>
       <c r="C5" t="n">
-        <v>2536</v>
+        <v>2494</v>
       </c>
       <c r="D5" t="n">
-        <v>1548</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>1434</v>
+        <v>1134</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>692</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5789</v>
+        <v>5244</v>
       </c>
       <c r="C2" t="n">
-        <v>9725</v>
+        <v>7950</v>
       </c>
       <c r="D2" t="n">
-        <v>19597</v>
+        <v>22836</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4239</v>
+        <v>4663</v>
       </c>
       <c r="C3" t="n">
-        <v>6475</v>
+        <v>6904</v>
       </c>
       <c r="D3" t="n">
-        <v>9976</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3009</v>
+        <v>3051</v>
       </c>
       <c r="C4" t="n">
-        <v>4154</v>
+        <v>5065</v>
       </c>
       <c r="D4" t="n">
-        <v>4757</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>1644</v>
       </c>
       <c r="C5" t="n">
-        <v>3397</v>
+        <v>3681</v>
       </c>
       <c r="D5" t="n">
-        <v>1962</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>752</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>2020</v>
+        <v>1851</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>1091</v>
+        <v>797</v>
       </c>
       <c r="D7" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>501</v>
+        <v>329</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_77_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6264</v>
+        <v>4743</v>
       </c>
       <c r="C2" t="n">
-        <v>5930</v>
+        <v>11212</v>
       </c>
       <c r="D2" t="n">
-        <v>23845</v>
+        <v>27575</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4075</v>
+        <v>2697</v>
       </c>
       <c r="C3" t="n">
-        <v>6480</v>
+        <v>4646</v>
       </c>
       <c r="D3" t="n">
-        <v>14054</v>
+        <v>8884</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3283</v>
+        <v>2293</v>
       </c>
       <c r="C4" t="n">
-        <v>5930</v>
+        <v>4670</v>
       </c>
       <c r="D4" t="n">
-        <v>7609</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>1532</v>
       </c>
       <c r="C5" t="n">
-        <v>4273</v>
+        <v>4917</v>
       </c>
       <c r="D5" t="n">
-        <v>3142</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1146</v>
+        <v>888</v>
       </c>
       <c r="C6" t="n">
-        <v>2744</v>
+        <v>4442</v>
       </c>
       <c r="D6" t="n">
-        <v>1294</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>554</v>
+        <v>417</v>
       </c>
       <c r="C7" t="n">
-        <v>1313</v>
+        <v>2840</v>
       </c>
       <c r="D7" t="n">
-        <v>686</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="C8" t="n">
-        <v>545</v>
+        <v>1324</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8696</v>
+        <v>4754</v>
       </c>
       <c r="C2" t="n">
-        <v>6986</v>
+        <v>14264</v>
       </c>
       <c r="D2" t="n">
-        <v>22065</v>
+        <v>33769</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4118</v>
+        <v>2911</v>
       </c>
       <c r="C3" t="n">
-        <v>5482</v>
+        <v>6669</v>
       </c>
       <c r="D3" t="n">
-        <v>14441</v>
+        <v>10828</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3108</v>
+        <v>2114</v>
       </c>
       <c r="C4" t="n">
-        <v>6013</v>
+        <v>4516</v>
       </c>
       <c r="D4" t="n">
-        <v>8356</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2279</v>
+        <v>1644</v>
       </c>
       <c r="C5" t="n">
-        <v>4963</v>
+        <v>4700</v>
       </c>
       <c r="D5" t="n">
-        <v>3775</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1380</v>
+        <v>1068</v>
       </c>
       <c r="C6" t="n">
-        <v>3380</v>
+        <v>4565</v>
       </c>
       <c r="D6" t="n">
-        <v>1547</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>724</v>
+        <v>550</v>
       </c>
       <c r="C7" t="n">
-        <v>1957</v>
+        <v>3545</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>316</v>
+        <v>231</v>
       </c>
       <c r="C8" t="n">
-        <v>870</v>
+        <v>1949</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>386</v>
+        <v>836</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9763</v>
+        <v>6220</v>
       </c>
       <c r="C2" t="n">
-        <v>7522</v>
+        <v>16878</v>
       </c>
       <c r="D2" t="n">
-        <v>25098</v>
+        <v>26431</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4818</v>
+        <v>2969</v>
       </c>
       <c r="C3" t="n">
-        <v>5412</v>
+        <v>8656</v>
       </c>
       <c r="D3" t="n">
-        <v>14469</v>
+        <v>12887</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3001</v>
+        <v>2070</v>
       </c>
       <c r="C4" t="n">
-        <v>5595</v>
+        <v>5352</v>
       </c>
       <c r="D4" t="n">
-        <v>9036</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2327</v>
+        <v>1635</v>
       </c>
       <c r="C5" t="n">
-        <v>5313</v>
+        <v>4481</v>
       </c>
       <c r="D5" t="n">
-        <v>4283</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1586</v>
+        <v>1182</v>
       </c>
       <c r="C6" t="n">
-        <v>3969</v>
+        <v>4534</v>
       </c>
       <c r="D6" t="n">
-        <v>1847</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>887</v>
+        <v>676</v>
       </c>
       <c r="C7" t="n">
-        <v>2522</v>
+        <v>3953</v>
       </c>
       <c r="D7" t="n">
-        <v>864</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>426</v>
+        <v>314</v>
       </c>
       <c r="C8" t="n">
-        <v>1306</v>
+        <v>2539</v>
       </c>
       <c r="D8" t="n">
-        <v>501</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>567</v>
+        <v>1241</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>513</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>235</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>89</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8847</v>
+        <v>5639</v>
       </c>
       <c r="C2" t="n">
-        <v>5114</v>
+        <v>11612</v>
       </c>
       <c r="D2" t="n">
-        <v>20634</v>
+        <v>21763</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5635</v>
+        <v>3635</v>
       </c>
       <c r="C3" t="n">
-        <v>8354</v>
+        <v>12409</v>
       </c>
       <c r="D3" t="n">
-        <v>16023</v>
+        <v>13343</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2150</v>
+        <v>1510</v>
       </c>
       <c r="C4" t="n">
-        <v>8215</v>
+        <v>7230</v>
       </c>
       <c r="D4" t="n">
-        <v>8945</v>
+        <v>4887</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>1092</v>
       </c>
       <c r="C5" t="n">
-        <v>3889</v>
+        <v>4443</v>
       </c>
       <c r="D5" t="n">
-        <v>2961</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>819</v>
+        <v>624</v>
       </c>
       <c r="C6" t="n">
-        <v>2471</v>
+        <v>3873</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>1279</v>
+        <v>2488</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>555</v>
+        <v>1216</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -1867,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>87</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5326</v>
+        <v>3450</v>
       </c>
       <c r="C2" t="n">
-        <v>2906</v>
+        <v>4994</v>
       </c>
       <c r="D2" t="n">
-        <v>14863</v>
+        <v>15282</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6022</v>
+        <v>3848</v>
       </c>
       <c r="C3" t="n">
-        <v>6217</v>
+        <v>10932</v>
       </c>
       <c r="D3" t="n">
-        <v>15727</v>
+        <v>13847</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3035</v>
+        <v>2030</v>
       </c>
       <c r="C4" t="n">
-        <v>8346</v>
+        <v>9743</v>
       </c>
       <c r="D4" t="n">
-        <v>9931</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>1186</v>
       </c>
       <c r="C5" t="n">
-        <v>5822</v>
+        <v>5687</v>
       </c>
       <c r="D5" t="n">
-        <v>3674</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>986</v>
+        <v>739</v>
       </c>
       <c r="C6" t="n">
-        <v>3124</v>
+        <v>4263</v>
       </c>
       <c r="D6" t="n">
-        <v>1063</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>369</v>
+        <v>271</v>
       </c>
       <c r="C7" t="n">
-        <v>1705</v>
+        <v>3072</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>767</v>
+        <v>1585</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>553</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6086</v>
+        <v>3437</v>
       </c>
       <c r="C2" t="n">
-        <v>8003</v>
+        <v>10619</v>
       </c>
       <c r="D2" t="n">
-        <v>16774</v>
+        <v>16479</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4807</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>4096</v>
+        <v>7284</v>
       </c>
       <c r="D3" t="n">
-        <v>14520</v>
+        <v>13111</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3706</v>
+        <v>2416</v>
       </c>
       <c r="C4" t="n">
-        <v>7109</v>
+        <v>10111</v>
       </c>
       <c r="D4" t="n">
-        <v>10630</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1989</v>
+        <v>1369</v>
       </c>
       <c r="C5" t="n">
-        <v>6968</v>
+        <v>7437</v>
       </c>
       <c r="D5" t="n">
-        <v>4583</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>4310</v>
+        <v>4892</v>
       </c>
       <c r="D6" t="n">
-        <v>1449</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>2346</v>
+        <v>3572</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1160</v>
+        <v>2197</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>947</v>
       </c>
       <c r="D9" t="n">
         <v>265</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>347</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3580</v>
+        <v>2047</v>
       </c>
       <c r="C2" t="n">
-        <v>3674</v>
+        <v>5041</v>
       </c>
       <c r="D2" t="n">
-        <v>11574</v>
+        <v>11498</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4982</v>
+        <v>3062</v>
       </c>
       <c r="C3" t="n">
-        <v>5308</v>
+        <v>8168</v>
       </c>
       <c r="D3" t="n">
-        <v>14423</v>
+        <v>13167</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4098</v>
+        <v>2666</v>
       </c>
       <c r="C4" t="n">
-        <v>6631</v>
+        <v>9975</v>
       </c>
       <c r="D4" t="n">
-        <v>11234</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2065</v>
+        <v>1445</v>
       </c>
       <c r="C5" t="n">
-        <v>8068</v>
+        <v>9227</v>
       </c>
       <c r="D5" t="n">
-        <v>4920</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>5149</v>
+        <v>5899</v>
       </c>
       <c r="D6" t="n">
-        <v>1408</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>2336</v>
+        <v>3852</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>1573</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>253</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4161</v>
+        <v>2577</v>
       </c>
       <c r="C2" t="n">
-        <v>4105</v>
+        <v>12206</v>
       </c>
       <c r="D2" t="n">
-        <v>13572</v>
+        <v>9489</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3749</v>
+        <v>2272</v>
       </c>
       <c r="C3" t="n">
-        <v>4046</v>
+        <v>6053</v>
       </c>
       <c r="D3" t="n">
-        <v>13066</v>
+        <v>12181</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3932</v>
+        <v>2467</v>
       </c>
       <c r="C4" t="n">
-        <v>5921</v>
+        <v>8934</v>
       </c>
       <c r="D4" t="n">
-        <v>11412</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2554</v>
+        <v>1716</v>
       </c>
       <c r="C5" t="n">
-        <v>7329</v>
+        <v>9453</v>
       </c>
       <c r="D5" t="n">
-        <v>5787</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1267</v>
+        <v>895</v>
       </c>
       <c r="C6" t="n">
-        <v>6385</v>
+        <v>7277</v>
       </c>
       <c r="D6" t="n">
-        <v>1861</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>3488</v>
+        <v>4728</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1428</v>
+        <v>2407</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>453</v>
+        <v>736</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3016</v>
+        <v>1675</v>
       </c>
       <c r="C2" t="n">
-        <v>2704</v>
+        <v>6984</v>
       </c>
       <c r="D2" t="n">
-        <v>10007</v>
+        <v>8332</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3402</v>
+        <v>2075</v>
       </c>
       <c r="C3" t="n">
-        <v>3691</v>
+        <v>7627</v>
       </c>
       <c r="D3" t="n">
-        <v>12415</v>
+        <v>11236</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3569</v>
+        <v>2221</v>
       </c>
       <c r="C4" t="n">
-        <v>5194</v>
+        <v>7871</v>
       </c>
       <c r="D4" t="n">
-        <v>11396</v>
+        <v>8663</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2823</v>
+        <v>1836</v>
       </c>
       <c r="C5" t="n">
-        <v>6944</v>
+        <v>9349</v>
       </c>
       <c r="D5" t="n">
-        <v>6370</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1490</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>6944</v>
+        <v>8233</v>
       </c>
       <c r="D6" t="n">
-        <v>2214</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>4401</v>
+        <v>5649</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1928</v>
+        <v>3002</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>538</v>
+        <v>825</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4717</v>
+        <v>2489</v>
       </c>
       <c r="C2" t="n">
-        <v>6166</v>
+        <v>20850</v>
       </c>
       <c r="D2" t="n">
-        <v>15278</v>
+        <v>13382</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2747</v>
+        <v>1635</v>
       </c>
       <c r="C3" t="n">
-        <v>2922</v>
+        <v>6649</v>
       </c>
       <c r="D3" t="n">
-        <v>11331</v>
+        <v>10276</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3050</v>
+        <v>1887</v>
       </c>
       <c r="C4" t="n">
-        <v>4436</v>
+        <v>7533</v>
       </c>
       <c r="D4" t="n">
-        <v>11196</v>
+        <v>8662</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2807</v>
+        <v>1793</v>
       </c>
       <c r="C5" t="n">
-        <v>6077</v>
+        <v>8572</v>
       </c>
       <c r="D5" t="n">
-        <v>6790</v>
+        <v>4414</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1812</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>6884</v>
+        <v>8583</v>
       </c>
       <c r="D6" t="n">
-        <v>2743</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>641</v>
+        <v>423</v>
       </c>
       <c r="C7" t="n">
-        <v>5414</v>
+        <v>6639</v>
       </c>
       <c r="D7" t="n">
-        <v>978</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>2799</v>
+        <v>3882</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1006</v>
+        <v>1515</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3711,7 +3711,7 @@
         <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6977</v>
+        <v>4632</v>
       </c>
       <c r="C2" t="n">
-        <v>3011</v>
+        <v>12355</v>
       </c>
       <c r="D2" t="n">
-        <v>19542</v>
+        <v>5372</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3377</v>
+        <v>1817</v>
       </c>
       <c r="C2" t="n">
-        <v>3502</v>
+        <v>12344</v>
       </c>
       <c r="D2" t="n">
-        <v>11244</v>
+        <v>9956</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3717</v>
+        <v>2199</v>
       </c>
       <c r="C3" t="n">
-        <v>3927</v>
+        <v>10281</v>
       </c>
       <c r="D3" t="n">
-        <v>12607</v>
+        <v>11279</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4152</v>
+        <v>2620</v>
       </c>
       <c r="C4" t="n">
-        <v>6433</v>
+        <v>10550</v>
       </c>
       <c r="D4" t="n">
-        <v>11560</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1752</v>
+        <v>1133</v>
       </c>
       <c r="C5" t="n">
-        <v>9296</v>
+        <v>12246</v>
       </c>
       <c r="D5" t="n">
-        <v>6298</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>592</v>
+        <v>390</v>
       </c>
       <c r="C6" t="n">
-        <v>6722</v>
+        <v>8020</v>
       </c>
       <c r="D6" t="n">
-        <v>2177</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>2743</v>
+        <v>3804</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>985</v>
+        <v>1484</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>395</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4319,7 +4319,7 @@
         <v>155</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7665</v>
+        <v>6043</v>
       </c>
       <c r="C2" t="n">
-        <v>3578</v>
+        <v>8764</v>
       </c>
       <c r="D2" t="n">
-        <v>16917</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2963</v>
+        <v>1969</v>
       </c>
       <c r="C3" t="n">
-        <v>1517</v>
+        <v>6226</v>
       </c>
       <c r="D3" t="n">
-        <v>3922</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5137</v>
+        <v>3898</v>
       </c>
       <c r="C2" t="n">
-        <v>7173</v>
+        <v>10190</v>
       </c>
       <c r="D2" t="n">
-        <v>22096</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4364</v>
+        <v>3287</v>
       </c>
       <c r="C3" t="n">
-        <v>2314</v>
+        <v>6607</v>
       </c>
       <c r="D3" t="n">
-        <v>5816</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1321</v>
+        <v>889</v>
       </c>
       <c r="C4" t="n">
-        <v>933</v>
+        <v>3690</v>
       </c>
       <c r="D4" t="n">
-        <v>1971</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5218</v>
+        <v>5400</v>
       </c>
       <c r="C2" t="n">
-        <v>6217</v>
+        <v>10315</v>
       </c>
       <c r="D2" t="n">
-        <v>25285</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3909</v>
+        <v>2956</v>
       </c>
       <c r="C3" t="n">
-        <v>4296</v>
+        <v>7410</v>
       </c>
       <c r="D3" t="n">
-        <v>8002</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2407</v>
+        <v>1773</v>
       </c>
       <c r="C4" t="n">
-        <v>1695</v>
+        <v>5265</v>
       </c>
       <c r="D4" t="n">
-        <v>2649</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>603</v>
+        <v>418</v>
       </c>
       <c r="C5" t="n">
-        <v>606</v>
+        <v>2114</v>
       </c>
       <c r="D5" t="n">
-        <v>1281</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5738</v>
+        <v>4500</v>
       </c>
       <c r="C2" t="n">
-        <v>9453</v>
+        <v>6338</v>
       </c>
       <c r="D2" t="n">
-        <v>25782</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3727</v>
+        <v>3347</v>
       </c>
       <c r="C3" t="n">
-        <v>4599</v>
+        <v>7751</v>
       </c>
       <c r="D3" t="n">
-        <v>10065</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2693</v>
+        <v>1989</v>
       </c>
       <c r="C4" t="n">
-        <v>3041</v>
+        <v>6308</v>
       </c>
       <c r="D4" t="n">
-        <v>3519</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1234</v>
+        <v>899</v>
       </c>
       <c r="C5" t="n">
-        <v>1168</v>
+        <v>3703</v>
       </c>
       <c r="D5" t="n">
-        <v>1491</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>322</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>453</v>
+        <v>1199</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8026</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="n">
-        <v>6993</v>
+        <v>5211</v>
       </c>
       <c r="D2" t="n">
-        <v>23961</v>
+        <v>17517</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3464</v>
+        <v>2845</v>
       </c>
       <c r="C3" t="n">
-        <v>5799</v>
+        <v>5774</v>
       </c>
       <c r="D3" t="n">
-        <v>11050</v>
+        <v>4717</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1980</v>
+        <v>1654</v>
       </c>
       <c r="C4" t="n">
-        <v>3171</v>
+        <v>5752</v>
       </c>
       <c r="D4" t="n">
-        <v>3989</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1025</v>
+        <v>747</v>
       </c>
       <c r="C5" t="n">
-        <v>1580</v>
+        <v>3690</v>
       </c>
       <c r="D5" t="n">
-        <v>1472</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>371</v>
+        <v>268</v>
       </c>
       <c r="C6" t="n">
-        <v>545</v>
+        <v>1632</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>257</v>
+        <v>489</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
         <v>362</v>
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6455</v>
+        <v>4715</v>
       </c>
       <c r="C2" t="n">
-        <v>9972</v>
+        <v>5810</v>
       </c>
       <c r="D2" t="n">
-        <v>25106</v>
+        <v>13716</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4790</v>
+        <v>3186</v>
       </c>
       <c r="C3" t="n">
-        <v>5584</v>
+        <v>4677</v>
       </c>
       <c r="D3" t="n">
-        <v>12491</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2373</v>
+        <v>1950</v>
       </c>
       <c r="C4" t="n">
-        <v>4719</v>
+        <v>5645</v>
       </c>
       <c r="D4" t="n">
-        <v>5359</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>1070</v>
       </c>
       <c r="C5" t="n">
-        <v>2494</v>
+        <v>4820</v>
       </c>
       <c r="D5" t="n">
-        <v>1934</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>651</v>
+        <v>466</v>
       </c>
       <c r="C6" t="n">
-        <v>1134</v>
+        <v>2777</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>1122</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>368</v>
       </c>
       <c r="D8" t="n">
         <v>386</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5244</v>
+        <v>3285</v>
       </c>
       <c r="C2" t="n">
-        <v>7950</v>
+        <v>6071</v>
       </c>
       <c r="D2" t="n">
-        <v>22836</v>
+        <v>22335</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4663</v>
+        <v>3232</v>
       </c>
       <c r="C3" t="n">
-        <v>6904</v>
+        <v>4583</v>
       </c>
       <c r="D3" t="n">
-        <v>13610</v>
+        <v>7201</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3051</v>
+        <v>2210</v>
       </c>
       <c r="C4" t="n">
-        <v>5065</v>
+        <v>4979</v>
       </c>
       <c r="D4" t="n">
-        <v>6513</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1644</v>
+        <v>1314</v>
       </c>
       <c r="C5" t="n">
-        <v>3681</v>
+        <v>5171</v>
       </c>
       <c r="D5" t="n">
-        <v>2532</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>695</v>
       </c>
       <c r="C6" t="n">
-        <v>1851</v>
+        <v>3824</v>
       </c>
       <c r="D6" t="n">
-        <v>1084</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>797</v>
+        <v>1970</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>329</v>
+        <v>752</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_77_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4743</v>
+        <v>1345</v>
       </c>
       <c r="C2" t="n">
-        <v>11212</v>
+        <v>3729</v>
       </c>
       <c r="D2" t="n">
-        <v>27575</v>
+        <v>13466</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2697</v>
+        <v>2236</v>
       </c>
       <c r="C3" t="n">
-        <v>4646</v>
+        <v>9829</v>
       </c>
       <c r="D3" t="n">
-        <v>8884</v>
+        <v>13641</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2293</v>
+        <v>1417</v>
       </c>
       <c r="C4" t="n">
-        <v>4670</v>
+        <v>13525</v>
       </c>
       <c r="D4" t="n">
-        <v>3701</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1532</v>
+        <v>647</v>
       </c>
       <c r="C5" t="n">
-        <v>4917</v>
+        <v>8619</v>
       </c>
       <c r="D5" t="n">
-        <v>1615</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>888</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>4442</v>
+        <v>3500</v>
       </c>
       <c r="D6" t="n">
-        <v>913</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>2840</v>
+        <v>1090</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1324</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4754</v>
+        <v>1841</v>
       </c>
       <c r="C2" t="n">
-        <v>14264</v>
+        <v>6289</v>
       </c>
       <c r="D2" t="n">
-        <v>33769</v>
+        <v>12715</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2911</v>
+        <v>1567</v>
       </c>
       <c r="C3" t="n">
-        <v>6669</v>
+        <v>6080</v>
       </c>
       <c r="D3" t="n">
-        <v>10828</v>
+        <v>12808</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2114</v>
+        <v>1536</v>
       </c>
       <c r="C4" t="n">
-        <v>4516</v>
+        <v>11528</v>
       </c>
       <c r="D4" t="n">
-        <v>4434</v>
+        <v>7387</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1644</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>4700</v>
+        <v>10747</v>
       </c>
       <c r="D5" t="n">
-        <v>1870</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1068</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>4565</v>
+        <v>5809</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>550</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>3545</v>
+        <v>2139</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1949</v>
+        <v>665</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>836</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6220</v>
+        <v>1049</v>
       </c>
       <c r="C2" t="n">
-        <v>16878</v>
+        <v>2961</v>
       </c>
       <c r="D2" t="n">
-        <v>26431</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2969</v>
+        <v>1575</v>
       </c>
       <c r="C3" t="n">
-        <v>8656</v>
+        <v>5957</v>
       </c>
       <c r="D3" t="n">
-        <v>12887</v>
+        <v>12490</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2070</v>
+        <v>1653</v>
       </c>
       <c r="C4" t="n">
-        <v>5352</v>
+        <v>10675</v>
       </c>
       <c r="D4" t="n">
-        <v>5177</v>
+        <v>8133</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1635</v>
+        <v>822</v>
       </c>
       <c r="C5" t="n">
-        <v>4481</v>
+        <v>12417</v>
       </c>
       <c r="D5" t="n">
-        <v>2182</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1182</v>
+        <v>278</v>
       </c>
       <c r="C6" t="n">
-        <v>4534</v>
+        <v>6697</v>
       </c>
       <c r="D6" t="n">
-        <v>1100</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>676</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3953</v>
+        <v>1875</v>
       </c>
       <c r="D7" t="n">
-        <v>695</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>314</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2539</v>
+        <v>502</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1241</v>
+        <v>223</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>513</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5639</v>
+        <v>682</v>
       </c>
       <c r="C2" t="n">
-        <v>11612</v>
+        <v>8877</v>
       </c>
       <c r="D2" t="n">
-        <v>21763</v>
+        <v>8930</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3635</v>
+        <v>1162</v>
       </c>
       <c r="C3" t="n">
-        <v>12409</v>
+        <v>4100</v>
       </c>
       <c r="D3" t="n">
-        <v>13343</v>
+        <v>11265</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1510</v>
+        <v>1424</v>
       </c>
       <c r="C4" t="n">
-        <v>7230</v>
+        <v>8233</v>
       </c>
       <c r="D4" t="n">
-        <v>4887</v>
+        <v>8554</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1092</v>
+        <v>1031</v>
       </c>
       <c r="C5" t="n">
-        <v>4443</v>
+        <v>11491</v>
       </c>
       <c r="D5" t="n">
-        <v>1664</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>624</v>
+        <v>422</v>
       </c>
       <c r="C6" t="n">
-        <v>3873</v>
+        <v>9182</v>
       </c>
       <c r="D6" t="n">
-        <v>681</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>2488</v>
+        <v>3801</v>
       </c>
       <c r="D7" t="n">
-        <v>456</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1216</v>
+        <v>996</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>68</v>
+      </c>
+      <c r="D14" t="n">
         <v>66</v>
-      </c>
-      <c r="D14" t="n">
-        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3450</v>
+        <v>378</v>
       </c>
       <c r="C2" t="n">
-        <v>4994</v>
+        <v>4740</v>
       </c>
       <c r="D2" t="n">
-        <v>15282</v>
+        <v>6929</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3848</v>
+        <v>883</v>
       </c>
       <c r="C3" t="n">
-        <v>10932</v>
+        <v>5478</v>
       </c>
       <c r="D3" t="n">
-        <v>13847</v>
+        <v>10371</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2030</v>
+        <v>1243</v>
       </c>
       <c r="C4" t="n">
-        <v>9743</v>
+        <v>6632</v>
       </c>
       <c r="D4" t="n">
-        <v>6003</v>
+        <v>8822</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1186</v>
+        <v>1095</v>
       </c>
       <c r="C5" t="n">
-        <v>5687</v>
+        <v>10425</v>
       </c>
       <c r="D5" t="n">
-        <v>2047</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>739</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>4263</v>
+        <v>10368</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>271</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3072</v>
+        <v>5325</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1585</v>
+        <v>1511</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>553</v>
+        <v>377</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3437</v>
+        <v>853</v>
       </c>
       <c r="C2" t="n">
-        <v>10619</v>
+        <v>12957</v>
       </c>
       <c r="D2" t="n">
-        <v>16479</v>
+        <v>14486</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3093</v>
+        <v>593</v>
       </c>
       <c r="C3" t="n">
-        <v>7284</v>
+        <v>4613</v>
       </c>
       <c r="D3" t="n">
-        <v>13111</v>
+        <v>9294</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2416</v>
+        <v>980</v>
       </c>
       <c r="C4" t="n">
-        <v>10111</v>
+        <v>6006</v>
       </c>
       <c r="D4" t="n">
-        <v>7100</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1369</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="n">
-        <v>7437</v>
+        <v>8678</v>
       </c>
       <c r="D5" t="n">
-        <v>2592</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>660</v>
       </c>
       <c r="C6" t="n">
-        <v>4892</v>
+        <v>10302</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
-        <v>3572</v>
+        <v>7253</v>
       </c>
       <c r="D7" t="n">
-        <v>533</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>2197</v>
+        <v>2833</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>947</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" t="n">
         <v>53</v>
-      </c>
-      <c r="D14" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2047</v>
+        <v>614</v>
       </c>
       <c r="C2" t="n">
-        <v>5041</v>
+        <v>7463</v>
       </c>
       <c r="D2" t="n">
-        <v>11498</v>
+        <v>10778</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3062</v>
+        <v>890</v>
       </c>
       <c r="C3" t="n">
-        <v>8168</v>
+        <v>6888</v>
       </c>
       <c r="D3" t="n">
-        <v>13167</v>
+        <v>10323</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2666</v>
+        <v>1465</v>
       </c>
       <c r="C4" t="n">
-        <v>9975</v>
+        <v>8957</v>
       </c>
       <c r="D4" t="n">
-        <v>7769</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1445</v>
+        <v>629</v>
       </c>
       <c r="C5" t="n">
-        <v>9227</v>
+        <v>13759</v>
       </c>
       <c r="D5" t="n">
-        <v>2771</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>704</v>
+        <v>196</v>
       </c>
       <c r="C6" t="n">
-        <v>5899</v>
+        <v>9026</v>
       </c>
       <c r="D6" t="n">
-        <v>966</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>3852</v>
+        <v>2776</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1573</v>
+        <v>717</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>256</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>51</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2577</v>
+        <v>301</v>
       </c>
       <c r="C2" t="n">
-        <v>12206</v>
+        <v>5007</v>
       </c>
       <c r="D2" t="n">
-        <v>9489</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2272</v>
+        <v>661</v>
       </c>
       <c r="C3" t="n">
-        <v>6053</v>
+        <v>6338</v>
       </c>
       <c r="D3" t="n">
-        <v>12181</v>
+        <v>9671</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2467</v>
+        <v>1012</v>
       </c>
       <c r="C4" t="n">
-        <v>8934</v>
+        <v>7564</v>
       </c>
       <c r="D4" t="n">
-        <v>8361</v>
+        <v>8490</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1716</v>
+        <v>650</v>
       </c>
       <c r="C5" t="n">
-        <v>9453</v>
+        <v>10268</v>
       </c>
       <c r="D5" t="n">
-        <v>3406</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>895</v>
+        <v>195</v>
       </c>
       <c r="C6" t="n">
-        <v>7277</v>
+        <v>8953</v>
       </c>
       <c r="D6" t="n">
-        <v>1196</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>4728</v>
+        <v>3641</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>2407</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>736</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1675</v>
+        <v>314</v>
       </c>
       <c r="C2" t="n">
-        <v>6984</v>
+        <v>19139</v>
       </c>
       <c r="D2" t="n">
-        <v>8332</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2075</v>
+        <v>421</v>
       </c>
       <c r="C3" t="n">
-        <v>7627</v>
+        <v>5022</v>
       </c>
       <c r="D3" t="n">
-        <v>11236</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2221</v>
+        <v>756</v>
       </c>
       <c r="C4" t="n">
-        <v>7871</v>
+        <v>6782</v>
       </c>
       <c r="D4" t="n">
-        <v>8663</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1836</v>
+        <v>725</v>
       </c>
       <c r="C5" t="n">
-        <v>9349</v>
+        <v>8730</v>
       </c>
       <c r="D5" t="n">
-        <v>3891</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>343</v>
       </c>
       <c r="C6" t="n">
-        <v>8233</v>
+        <v>9567</v>
       </c>
       <c r="D6" t="n">
-        <v>1375</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>235</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>5649</v>
+        <v>6034</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>3002</v>
+        <v>2074</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>825</v>
+        <v>494</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2489</v>
+        <v>543</v>
       </c>
       <c r="C2" t="n">
-        <v>20850</v>
+        <v>19144</v>
       </c>
       <c r="D2" t="n">
-        <v>13382</v>
+        <v>12451</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1635</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>6649</v>
+        <v>9856</v>
       </c>
       <c r="D3" t="n">
-        <v>10276</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1887</v>
+        <v>542</v>
       </c>
       <c r="C4" t="n">
-        <v>7533</v>
+        <v>5829</v>
       </c>
       <c r="D4" t="n">
-        <v>8662</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1793</v>
+        <v>673</v>
       </c>
       <c r="C5" t="n">
-        <v>8572</v>
+        <v>7688</v>
       </c>
       <c r="D5" t="n">
-        <v>4414</v>
+        <v>5167</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>447</v>
       </c>
       <c r="C6" t="n">
-        <v>8583</v>
+        <v>9031</v>
       </c>
       <c r="D6" t="n">
-        <v>1671</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>6639</v>
+        <v>7520</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>3882</v>
+        <v>3664</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1515</v>
+        <v>1097</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>404</v>
+        <v>276</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4632</v>
+        <v>4790</v>
       </c>
       <c r="C2" t="n">
-        <v>12355</v>
+        <v>25498</v>
       </c>
       <c r="D2" t="n">
-        <v>5372</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1817</v>
+        <v>702</v>
       </c>
       <c r="C2" t="n">
-        <v>12344</v>
+        <v>27163</v>
       </c>
       <c r="D2" t="n">
-        <v>9956</v>
+        <v>18872</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2199</v>
+        <v>326</v>
       </c>
       <c r="C3" t="n">
-        <v>10281</v>
+        <v>11920</v>
       </c>
       <c r="D3" t="n">
-        <v>11279</v>
+        <v>8190</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>398</v>
       </c>
       <c r="C4" t="n">
-        <v>10550</v>
+        <v>7275</v>
       </c>
       <c r="D4" t="n">
-        <v>8709</v>
+        <v>7834</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1133</v>
+        <v>579</v>
       </c>
       <c r="C5" t="n">
-        <v>12246</v>
+        <v>6796</v>
       </c>
       <c r="D5" t="n">
-        <v>4013</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>390</v>
+        <v>483</v>
       </c>
       <c r="C6" t="n">
-        <v>8020</v>
+        <v>8365</v>
       </c>
       <c r="D6" t="n">
-        <v>1428</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>3804</v>
+        <v>8079</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1484</v>
+        <v>4987</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>395</v>
+        <v>1977</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>538</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6043</v>
+        <v>4986</v>
       </c>
       <c r="C2" t="n">
-        <v>8764</v>
+        <v>18180</v>
       </c>
       <c r="D2" t="n">
-        <v>6480</v>
+        <v>34066</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1969</v>
+        <v>1545</v>
       </c>
       <c r="C3" t="n">
-        <v>6226</v>
+        <v>10069</v>
       </c>
       <c r="D3" t="n">
-        <v>1541</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3898</v>
+        <v>3266</v>
       </c>
       <c r="C2" t="n">
-        <v>10190</v>
+        <v>9299</v>
       </c>
       <c r="D2" t="n">
-        <v>7820</v>
+        <v>24289</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3287</v>
+        <v>2732</v>
       </c>
       <c r="C3" t="n">
-        <v>6607</v>
+        <v>12884</v>
       </c>
       <c r="D3" t="n">
-        <v>2257</v>
+        <v>7051</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>889</v>
+        <v>727</v>
       </c>
       <c r="C4" t="n">
-        <v>3690</v>
+        <v>6139</v>
       </c>
       <c r="D4" t="n">
-        <v>1491</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5400</v>
+        <v>3001</v>
       </c>
       <c r="C2" t="n">
-        <v>10315</v>
+        <v>8992</v>
       </c>
       <c r="D2" t="n">
-        <v>13004</v>
+        <v>25945</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2956</v>
+        <v>2470</v>
       </c>
       <c r="C3" t="n">
-        <v>7410</v>
+        <v>9410</v>
       </c>
       <c r="D3" t="n">
-        <v>2984</v>
+        <v>9301</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1773</v>
+        <v>1485</v>
       </c>
       <c r="C4" t="n">
-        <v>5265</v>
+        <v>9896</v>
       </c>
       <c r="D4" t="n">
-        <v>1592</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="C5" t="n">
-        <v>2114</v>
+        <v>3507</v>
       </c>
       <c r="D5" t="n">
-        <v>1194</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4500</v>
+        <v>2849</v>
       </c>
       <c r="C2" t="n">
-        <v>6338</v>
+        <v>14732</v>
       </c>
       <c r="D2" t="n">
-        <v>11010</v>
+        <v>23780</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3347</v>
+        <v>2243</v>
       </c>
       <c r="C3" t="n">
-        <v>7751</v>
+        <v>8003</v>
       </c>
       <c r="D3" t="n">
-        <v>4296</v>
+        <v>11176</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1989</v>
+        <v>1684</v>
       </c>
       <c r="C4" t="n">
-        <v>6308</v>
+        <v>9428</v>
       </c>
       <c r="D4" t="n">
-        <v>1797</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>899</v>
+        <v>751</v>
       </c>
       <c r="C5" t="n">
-        <v>3703</v>
+        <v>6746</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="C6" t="n">
-        <v>1199</v>
+        <v>1878</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>2473</v>
       </c>
       <c r="C2" t="n">
-        <v>5211</v>
+        <v>12042</v>
       </c>
       <c r="D2" t="n">
-        <v>17517</v>
+        <v>23112</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2845</v>
+        <v>2069</v>
       </c>
       <c r="C3" t="n">
-        <v>5774</v>
+        <v>9816</v>
       </c>
       <c r="D3" t="n">
-        <v>4717</v>
+        <v>12222</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="C4" t="n">
-        <v>5752</v>
+        <v>8520</v>
       </c>
       <c r="D4" t="n">
-        <v>1916</v>
+        <v>4829</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>747</v>
+        <v>1018</v>
       </c>
       <c r="C5" t="n">
-        <v>3690</v>
+        <v>7893</v>
       </c>
       <c r="D5" t="n">
-        <v>1026</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>388</v>
       </c>
       <c r="C6" t="n">
-        <v>1632</v>
+        <v>4083</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>489</v>
+        <v>1025</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4715</v>
+        <v>2726</v>
       </c>
       <c r="C2" t="n">
-        <v>5810</v>
+        <v>10664</v>
       </c>
       <c r="D2" t="n">
-        <v>13716</v>
+        <v>23359</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3186</v>
+        <v>1846</v>
       </c>
       <c r="C3" t="n">
-        <v>4677</v>
+        <v>9522</v>
       </c>
       <c r="D3" t="n">
-        <v>6520</v>
+        <v>12814</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1950</v>
+        <v>1560</v>
       </c>
       <c r="C4" t="n">
-        <v>5645</v>
+        <v>8845</v>
       </c>
       <c r="D4" t="n">
-        <v>2404</v>
+        <v>5771</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1070</v>
+        <v>1127</v>
       </c>
       <c r="C5" t="n">
-        <v>4820</v>
+        <v>8005</v>
       </c>
       <c r="D5" t="n">
-        <v>1174</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>466</v>
+        <v>581</v>
       </c>
       <c r="C6" t="n">
-        <v>2777</v>
+        <v>5614</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="C7" t="n">
-        <v>1122</v>
+        <v>2313</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>368</v>
+        <v>588</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
-        <v>151</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3285</v>
+        <v>2558</v>
       </c>
       <c r="C2" t="n">
-        <v>6071</v>
+        <v>7166</v>
       </c>
       <c r="D2" t="n">
-        <v>22335</v>
+        <v>18992</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3232</v>
+        <v>2524</v>
       </c>
       <c r="C3" t="n">
-        <v>4583</v>
+        <v>13987</v>
       </c>
       <c r="D3" t="n">
-        <v>7201</v>
+        <v>13713</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2210</v>
+        <v>1041</v>
       </c>
       <c r="C4" t="n">
-        <v>4979</v>
+        <v>12694</v>
       </c>
       <c r="D4" t="n">
-        <v>3121</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1314</v>
+        <v>536</v>
       </c>
       <c r="C5" t="n">
-        <v>5171</v>
+        <v>5501</v>
       </c>
       <c r="D5" t="n">
-        <v>1351</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>695</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>3824</v>
+        <v>2266</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1970</v>
+        <v>576</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>752</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>156</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
